--- a/web/public/forms/jugan-hoeuirok.xlsx
+++ b/web/public/forms/jugan-hoeuirok.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공사 회의록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공사 회의록'!$A$1:$X$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +36,53 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +91,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +115,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,29 +140,47 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,15 +576,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -559,7 +608,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -589,7 +638,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -619,7 +668,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -649,7 +698,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -712,23 +761,23 @@
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="9" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="L11" s="9" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="Q11" s="8" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
       <c r="T11" s="5" t="n"/>
@@ -738,23 +787,23 @@
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="G12" s="9" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="L12" s="9" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="Q12" s="8" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
@@ -764,23 +813,23 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="G13" s="9" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="L13" s="9" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="Q13" s="8" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
@@ -790,23 +839,23 @@
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="G14" s="9" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="9" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="Q14" s="8" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
@@ -816,23 +865,23 @@
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="9" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="L15" s="9" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="Q15" s="8" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
@@ -842,23 +891,23 @@
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="9" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="L16" s="9" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="Q16" s="8" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
@@ -915,267 +964,297 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="10">
+        <f>IF(C19="","",COUNTA(C19:C19))</f>
+        <v/>
+      </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="Q19" s="9" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="8" t="inlineStr"/>
+      <c r="T19" s="9" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="10">
+        <f>IF(C20="","",COUNTA(C19:C20))</f>
+        <v/>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="8" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="Q20" s="9" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="8" t="inlineStr"/>
+      <c r="T20" s="9" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr"/>
+      <c r="A21" s="10">
+        <f>IF(C21="","",COUNTA(C19:C21))</f>
+        <v/>
+      </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="n"/>
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="Q21" s="9" t="n"/>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
-      <c r="T21" s="8" t="inlineStr"/>
+      <c r="T21" s="9" t="n"/>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr"/>
+      <c r="A22" s="10">
+        <f>IF(C22="","",COUNTA(C19:C22))</f>
+        <v/>
+      </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="8" t="inlineStr"/>
+      <c r="Q22" s="9" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
-      <c r="T22" s="8" t="inlineStr"/>
+      <c r="T22" s="9" t="n"/>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr"/>
+      <c r="A23" s="10">
+        <f>IF(C23="","",COUNTA(C19:C23))</f>
+        <v/>
+      </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
-      <c r="J23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="n"/>
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="Q23" s="9" t="n"/>
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5" t="n"/>
-      <c r="T23" s="8" t="inlineStr"/>
+      <c r="T23" s="9" t="n"/>
       <c r="U23" s="5" t="n"/>
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr"/>
+      <c r="A24" s="10">
+        <f>IF(C24="","",COUNTA(C19:C24))</f>
+        <v/>
+      </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="n"/>
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="n"/>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="8" t="inlineStr"/>
+      <c r="Q24" s="9" t="n"/>
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5" t="n"/>
-      <c r="T24" s="8" t="inlineStr"/>
+      <c r="T24" s="9" t="n"/>
       <c r="U24" s="5" t="n"/>
       <c r="V24" s="5" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr"/>
+      <c r="A25" s="10">
+        <f>IF(C25="","",COUNTA(C19:C25))</f>
+        <v/>
+      </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
-      <c r="J25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="n"/>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="5" t="n"/>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="Q25" s="9" t="n"/>
       <c r="R25" s="5" t="n"/>
       <c r="S25" s="5" t="n"/>
-      <c r="T25" s="8" t="inlineStr"/>
+      <c r="T25" s="9" t="n"/>
       <c r="U25" s="5" t="n"/>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr"/>
+      <c r="A26" s="10">
+        <f>IF(C26="","",COUNTA(C19:C26))</f>
+        <v/>
+      </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
-      <c r="J26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="n"/>
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n"/>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="8" t="inlineStr"/>
+      <c r="Q26" s="9" t="n"/>
       <c r="R26" s="5" t="n"/>
       <c r="S26" s="5" t="n"/>
-      <c r="T26" s="8" t="inlineStr"/>
+      <c r="T26" s="9" t="n"/>
       <c r="U26" s="5" t="n"/>
       <c r="V26" s="5" t="n"/>
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="8" t="inlineStr"/>
+      <c r="A27" s="10">
+        <f>IF(C27="","",COUNTA(C19:C27))</f>
+        <v/>
+      </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
-      <c r="J27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="n"/>
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="Q27" s="9" t="n"/>
       <c r="R27" s="5" t="n"/>
       <c r="S27" s="5" t="n"/>
-      <c r="T27" s="8" t="inlineStr"/>
+      <c r="T27" s="9" t="n"/>
       <c r="U27" s="5" t="n"/>
       <c r="V27" s="5" t="n"/>
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="inlineStr"/>
+      <c r="A28" s="10">
+        <f>IF(C28="","",COUNTA(C19:C28))</f>
+        <v/>
+      </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="n"/>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
-      <c r="J28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="n"/>
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="8" t="inlineStr"/>
+      <c r="Q28" s="9" t="n"/>
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n"/>
-      <c r="T28" s="8" t="inlineStr"/>
+      <c r="T28" s="9" t="n"/>
       <c r="U28" s="5" t="n"/>
       <c r="V28" s="5" t="n"/>
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  지난 회의 미결 사항</t>
@@ -1186,7 +1265,7 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
@@ -1216,7 +1295,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
@@ -1238,52 +1317,62 @@
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="10" customHeight="1"/>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="K35" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="12" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>작성자</t>
         </is>
       </c>
-      <c r="S35" s="9" t="inlineStr">
+      <c r="Q35" s="14" t="n"/>
+      <c r="U35" s="15" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="K36" s="10" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="12" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S36" s="9" t="inlineStr">
+      <c r="Q36" s="14" t="n"/>
+      <c r="U36" s="15" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="6" customHeight="1"/>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="109">
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="L16:P16"/>
     <mergeCell ref="J21:P21"/>
-    <mergeCell ref="K36:R36"/>
     <mergeCell ref="C19:I19"/>
     <mergeCell ref="C28:I28"/>
     <mergeCell ref="A3:X3"/>
@@ -1291,6 +1380,7 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G13:K13"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A36:J36"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="A31:F31"/>
@@ -1301,12 +1391,14 @@
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="A40:X40"/>
     <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q35:T35"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="G16:K16"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="K35:P35"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="Q13:X13"/>
@@ -1315,14 +1407,13 @@
     <mergeCell ref="Q19:S19"/>
     <mergeCell ref="Q16:X16"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q36:T36"/>
     <mergeCell ref="T20:X20"/>
     <mergeCell ref="G11:K11"/>
     <mergeCell ref="L13:P13"/>
-    <mergeCell ref="K35:R35"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="L15:P15"/>
-    <mergeCell ref="S36:X36"/>
     <mergeCell ref="Q10:X10"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C20:I20"/>
@@ -1347,20 +1438,22 @@
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="L14:P14"/>
     <mergeCell ref="J28:P28"/>
-    <mergeCell ref="S35:X35"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="T21:X21"/>
+    <mergeCell ref="U36:X36"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="A39:X39"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="T18:X18"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="J18:P18"/>
@@ -1368,6 +1461,7 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="U35:X35"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="Q14:X14"/>
     <mergeCell ref="A18:B18"/>
@@ -1377,13 +1471,1087 @@
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="A34:X34"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K36:P36"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="C27:I27"/>
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="Q20:S20"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="G8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"주간 공정회의,월간 회의,착공 회의,임시 회의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>공  사  회  의  록</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  회의 일시</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>2026. 9. 28. 15:00</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  회의 장소</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>현장 사무실</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  회의 구분</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>주간 공정회의</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>소속</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>직위</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>서명</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>가나시 건설과</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>박감독</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>감독관</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>예시감리단</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>박감리</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>책임감리</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>(주)예시토건</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>나소장</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>안건 / 협의 내용</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>결정 사항</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>완료 기한</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10">
+        <f>IF(C19="","",COUNTA(C19:C19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>배수공 공정 지연 만회</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>10월 2개 조 투입</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>10. 31.</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10">
+        <f>IF(C20="","",COUNTA(C19:C20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>암거 B 벽체 타설 일정</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>10. 8. 타설</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>이감독</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>10. 8.</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10">
+        <f>IF(C21="","",COUNTA(C19:C21))</f>
+        <v/>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>우기 뒤 사면 점검</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>10. 2. 합동 점검</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="9" t="inlineStr">
+        <is>
+          <t>정안전</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>10. 2.</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10">
+        <f>IF(C22="","",COUNTA(C19:C22))</f>
+        <v/>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10">
+        <f>IF(C23="","",COUNTA(C19:C23))</f>
+        <v/>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="10">
+        <f>IF(C24="","",COUNTA(C19:C24))</f>
+        <v/>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="10">
+        <f>IF(C25="","",COUNTA(C19:C25))</f>
+        <v/>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="10">
+        <f>IF(C26="","",COUNTA(C19:C26))</f>
+        <v/>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10">
+        <f>IF(C27="","",COUNTA(C19:C27))</f>
+        <v/>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="10">
+        <f>IF(C28="","",COUNTA(C19:C28))</f>
+        <v/>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  지난 회의 미결 사항</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>관급 맨홀뚜껑 반입 일정(계속)</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  다음 회의</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>2026. 10. 5. 15:00 현장 사무실</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="10" customHeight="1"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="11" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="12" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>이영희</t>
+        </is>
+      </c>
+      <c r="U35" s="15" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="12" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q36" s="14" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U36" s="15" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="108">
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="L16:P16"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="G31:X31"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q35:T35"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="K35:P35"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="Q13:X13"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="Q16:X16"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q36:T36"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="L13:P13"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q10:X10"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="L10:P10"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="Q11:X11"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q12:X12"/>
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="L14:P14"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="T23:X23"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="A39:X39"/>
+    <mergeCell ref="T27:X27"/>
+    <mergeCell ref="T18:X18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="G30:X30"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="Q14:X14"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q15:X15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K36:P36"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="Q20:S20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="G8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"주간 공정회의,월간 회의,착공 회의,임시 회의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/jugan-hoeuirok.xlsx
+++ b/web/public/forms/jugan-hoeuirok.xlsx
@@ -579,7 +579,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="17" t="inlineStr">

--- a/web/public/forms/jugan-hoeuirok.xlsx
+++ b/web/public/forms/jugan-hoeuirok.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공사 회의록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공사 회의록'!$A$1:$X$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -178,9 +176,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,10 +959,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10">
-        <f>IF(C19="","",COUNTA(C19:C19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="5" t="n"/>
@@ -993,10 +985,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10">
-        <f>IF(C20="","",COUNTA(C19:C20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="10" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="5" t="n"/>
@@ -1022,10 +1011,7 @@
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10">
-        <f>IF(C21="","",COUNTA(C19:C21))</f>
-        <v/>
-      </c>
+      <c r="A21" s="10" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="5" t="n"/>
@@ -1051,10 +1037,7 @@
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10">
-        <f>IF(C22="","",COUNTA(C19:C22))</f>
-        <v/>
-      </c>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="5" t="n"/>
@@ -1080,10 +1063,7 @@
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10">
-        <f>IF(C23="","",COUNTA(C19:C23))</f>
-        <v/>
-      </c>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="5" t="n"/>
@@ -1109,10 +1089,7 @@
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10">
-        <f>IF(C24="","",COUNTA(C19:C24))</f>
-        <v/>
-      </c>
+      <c r="A24" s="10" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="5" t="n"/>
@@ -1138,10 +1115,7 @@
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10">
-        <f>IF(C25="","",COUNTA(C19:C25))</f>
-        <v/>
-      </c>
+      <c r="A25" s="10" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="5" t="n"/>
@@ -1167,10 +1141,7 @@
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10">
-        <f>IF(C26="","",COUNTA(C19:C26))</f>
-        <v/>
-      </c>
+      <c r="A26" s="10" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="5" t="n"/>
@@ -1196,10 +1167,7 @@
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10">
-        <f>IF(C27="","",COUNTA(C19:C27))</f>
-        <v/>
-      </c>
+      <c r="A27" s="10" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -1225,10 +1193,7 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="10">
-        <f>IF(C28="","",COUNTA(C19:C28))</f>
-        <v/>
-      </c>
+      <c r="A28" s="10" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -1352,6 +1317,7 @@
       </c>
     </row>
     <row r="37" ht="6" customHeight="1"/>
+    <row r="38"/>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
@@ -1487,1071 +1453,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>공  사  회  의  록</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  회의 일시</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>2026. 9. 28. 15:00</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  회의 장소</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>현장 사무실</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  회의 구분</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>주간 공정회의</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>소속</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>직위</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>서명</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>가나시 건설과</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>박감독</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>감독관</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="8" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>예시감리단</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>책임감리</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="8" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>(주)예시토건</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>나소장</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="8" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="8" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>안건 / 협의 내용</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>결정 사항</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>완료 기한</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10">
-        <f>IF(C19="","",COUNTA(C19:C19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>배수공 공정 지연 만회</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>10월 2개 조 투입</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>10. 31.</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10">
-        <f>IF(C20="","",COUNTA(C19:C20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>암거 B 벽체 타설 일정</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>10. 8. 타설</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>이감독</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>10. 8.</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10">
-        <f>IF(C21="","",COUNTA(C19:C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>우기 뒤 사면 점검</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>10. 2. 합동 점검</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="9" t="inlineStr">
-        <is>
-          <t>정안전</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="9" t="inlineStr">
-        <is>
-          <t>10. 2.</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10">
-        <f>IF(C22="","",COUNTA(C19:C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10">
-        <f>IF(C23="","",COUNTA(C19:C23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="9" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10">
-        <f>IF(C24="","",COUNTA(C19:C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="9" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10">
-        <f>IF(C25="","",COUNTA(C19:C25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="9" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10">
-        <f>IF(C26="","",COUNTA(C19:C26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="9" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10">
-        <f>IF(C27="","",COUNTA(C19:C27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="10">
-        <f>IF(C28="","",COUNTA(C19:C28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="9" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  지난 회의 미결 사항</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>관급 맨홀뚜껑 반입 일정(계속)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  다음 회의</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>2026. 10. 5. 15:00 현장 사무실</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="10" customHeight="1"/>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="11" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="12" t="inlineStr"/>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>작성자</t>
-        </is>
-      </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="U35" s="15" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="12" t="inlineStr"/>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q36" s="14" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U36" s="15" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="108">
-    <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="L16:P16"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="G31:X31"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q35:T35"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="K35:P35"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="Q13:X13"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="Q16:X16"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q36:T36"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L13:P13"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q10:X10"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="L10:P10"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="Q11:X11"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="L11:P11"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q12:X12"/>
-    <mergeCell ref="L12:P12"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="L14:P14"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="A39:X39"/>
-    <mergeCell ref="T27:X27"/>
-    <mergeCell ref="T18:X18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="G30:X30"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="Q14:X14"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q15:X15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="K36:P36"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="Q20:S20"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="G8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"주간 공정회의,월간 회의,착공 회의,임시 회의"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/jugan-hoeuirok.xlsx
+++ b/web/public/forms/jugan-hoeuirok.xlsx
@@ -574,7 +574,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
